--- a/EstablecimientoSalud/excels/LIMA-LIMA-LIMA.xlsx
+++ b/EstablecimientoSalud/excels/LIMA-LIMA-LIMA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>5990</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150108</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CHORRILLOS</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.1692159</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>5808</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150135</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SAN MARTIN DE PORRES</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-11.972234</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>6153</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.1776988</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>5825</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150139</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SANTA ROSA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-11.7848464</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>28380</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150115</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.0734497</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>6203</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.0531204</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>5639</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150128</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RIMAC</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.0168446</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>35003</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150113</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>JESUS MARIA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.0796889</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>5996</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.162636</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>5623</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-11.9558652</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>6113</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.1480219</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>6193</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.0512449</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.1167928</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>5847</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-12.0105371</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>26131</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150110</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COMAS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-11.9374701</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>35717</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>150136</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SAN MIGUEL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-12.08178235</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>12822</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>150141</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SURQUILLO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.11321922</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>5814</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>150102</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ANCON</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-11.77452348</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>6194</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.0367561</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>8292</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>150108</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CHORRILLOS</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-12.1601295</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-12.0359928</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>6189</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-12.0410293</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.1168591</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>15471</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>150131</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SAN ISIDRO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-12.1083451</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>15075</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-12.1096968</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>28678</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>150105</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>BREÑA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-12.0541636</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>28401</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-12.0556519</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>13012</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-12.1643037</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>6107</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-12.1358082</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>6151</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-12.1569104</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>13914</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>150128</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RIMAC</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-12.0282877</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>6202</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-12.05006736</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>6091</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-12.1590087</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>6099</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-12.1811992</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>6171</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-12.0537765</t>
@@ -2652,40 +2477,35 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>5743</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>150135</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SAN MARTIN DE PORRES</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-12.030943</t>
@@ -2714,40 +2534,35 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>9304</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-12.0550758</t>
@@ -2776,40 +2591,35 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>26205</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>150111</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>EL AGUSTINO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-12.0618186</t>
@@ -2838,40 +2648,35 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>27068</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-12.01673871</t>
@@ -2900,40 +2705,35 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>25226</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>150125</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PUENTE PIEDRA</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-11.93531354</t>
@@ -2962,40 +2762,35 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>8880</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-12.0590926</t>
@@ -3024,40 +2819,35 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>6133</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-12.2191614</t>
@@ -3086,40 +2876,35 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>6140</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-12.1733468</t>
@@ -3148,40 +2933,35 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>6145</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-12.2210199</t>
@@ -3210,40 +2990,35 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>5739</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>150106</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>CARABAYLLO</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-11.8770066</t>
@@ -3272,40 +3047,35 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>9163</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>150125</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>PUENTE PIEDRA</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-11.8628584</t>
@@ -3334,40 +3104,35 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>17391</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-12.05829209</t>
@@ -3396,40 +3161,35 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>6200</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>150122</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-12.1189648</t>
@@ -3458,40 +3218,35 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>6155</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-12.1418352</t>
@@ -3520,40 +3275,35 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>35008</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-12.02030225</t>
@@ -3582,40 +3332,35 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>36395</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-12.0658903</t>
@@ -3644,40 +3389,35 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>27181</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>150141</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>SURQUILLO</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-12.112988</t>
@@ -3706,40 +3446,35 @@
       <c r="K53" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>6196</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>150120</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>MAGDALENA DEL MAR</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-12.0886944</t>
@@ -3768,40 +3503,35 @@
       <c r="K54" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>6197</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>150131</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>SAN ISIDRO</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-12.1067332</t>
@@ -3830,40 +3560,35 @@
       <c r="K55" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>6188</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-12.0411673</t>
@@ -3892,40 +3617,35 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>6152</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-12.147521</t>
@@ -3954,40 +3674,35 @@
       <c r="K57" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>6198</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>150136</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>SAN MIGUEL</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>-12.0813992</t>
@@ -4016,40 +3731,35 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>8539</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-12.06264167</t>
@@ -4078,40 +3788,35 @@
       <c r="K59" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>7434</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-12.189694</t>
@@ -4140,40 +3845,35 @@
       <c r="K60" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>30839</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-12.0038187</t>
@@ -4202,40 +3902,35 @@
       <c r="K61" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>29166</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-12.0558075</t>
@@ -4264,40 +3959,35 @@
       <c r="K62" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>18171</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>150108</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CHORRILLOS</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>-12.1567124</t>
@@ -4326,40 +4016,35 @@
       <c r="K63" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>5629</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>-11.9370395</t>
@@ -4388,40 +4073,35 @@
       <c r="K64" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>8378</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>-12.1507658</t>
@@ -4450,40 +4130,35 @@
       <c r="K65" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>6191</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-12.0428657</t>
@@ -4512,40 +4187,35 @@
       <c r="K66" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>6097</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>150123</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>PACHACAMAC</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>-12.1874984</t>
@@ -4574,40 +4244,35 @@
       <c r="K67" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>6192</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-12.0509882</t>
@@ -4636,40 +4301,35 @@
       <c r="K68" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>5763</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>150110</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>COMAS</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>-11.9402602</t>
@@ -4698,40 +4358,35 @@
       <c r="K69" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>5819</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>150125</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>PUENTE PIEDRA</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>-11.92118965</t>
@@ -4760,40 +4415,35 @@
       <c r="K70" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>6084</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>150124</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>PUCUSANA</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>-12.48301</t>
@@ -4822,40 +4472,35 @@
       <c r="K71" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>9298</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>150122</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>-12.1241585</t>
@@ -4884,40 +4529,35 @@
       <c r="K72" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>6105</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>-12.1535138</t>
@@ -4946,40 +4586,35 @@
       <c r="K73" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>27726</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>-12.01734472</t>
@@ -5008,40 +4643,35 @@
       <c r="K74" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>25929</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>150113</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>JESUS MARIA</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>-12.0781849</t>
@@ -5070,40 +4700,35 @@
       <c r="K75" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>8709</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>-12.1521653</t>
@@ -5132,40 +4757,35 @@
       <c r="K76" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>5749</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>150135</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>SAN MARTIN DE PORRES</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>-12.028589</t>
@@ -5194,40 +4814,35 @@
       <c r="K77" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>34079</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>150119</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>LURIN</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-12.27200166</t>
@@ -5256,40 +4871,35 @@
       <c r="K78" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>35375</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>-12.05011982</t>
@@ -5318,40 +4928,35 @@
       <c r="K79" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>6186</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>-12.039118</t>
@@ -5380,40 +4985,35 @@
       <c r="K80" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>8445</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>-12.0493589</t>
@@ -5442,40 +5042,35 @@
       <c r="K81" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>35678</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>-12.0727243</t>
@@ -5504,40 +5099,35 @@
       <c r="K82" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>5965</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>-12.0606209</t>
@@ -5566,40 +5156,35 @@
       <c r="K83" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>29493</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>-12.04905784</t>
@@ -5628,11 +5213,6 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>150101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/LIMA-LIMA-LIMA.xlsx
+++ b/EstablecimientoSalud/excels/LIMA-LIMA-LIMA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
